--- a/data/qa/prospect_to_cash/estimate.xlsx
+++ b/data/qa/prospect_to_cash/estimate.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,126 +426,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:X8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>field</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>intent</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sub_intent</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>canonical_question</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>answer</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>keywords</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>route</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>source_reference</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>source_section</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>site_scope</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>security_scope</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>approval_status</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>effective_date</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>last_reviewed_date</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -542,7 +554,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QA-0003</t>
+          <t>KB-0052</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -552,50 +564,38 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Estimate Module</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Estimates</t>
-        </is>
-      </c>
+          <t>Estimate Module</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>HELP_GENERIC</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>definition</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>What is an Estimate?</t>
+          <t>What is an estimate and what information does it include?</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>An Estimate is a preliminary price and terms calculation prepared for a customer before a formal Quotation is issued.</t>
+          <t>An estimate holds the proposed items, quantities, price, terms, and dates used to quote a prospect or customer. Use Estimates for the header and Estimate Lines for item detail.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>estimate,quote draft</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>quote draft</t>
-        </is>
-      </c>
+          <t>estimate, Estimates form, items, price, terms</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>FAST_QA</t>
@@ -603,18 +603,16 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PTC Training Guide</t>
+          <t>estimate.md</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+          <t>Estimate Module &gt; Meaning, status, and forms</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -627,10 +625,14 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V2" t="b">
@@ -638,10 +640,598 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KB-0053</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Estimate Module</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Estimate Module</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HELP_FIELD</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>What do the different estimate statuses mean?</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Infor describes header states Working, Quoted, Planned, and History. Quoted means the estimate has been used to quote a price; it does not mean customer acceptance.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>estimate, status, Working, Quoted, Planned, History</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>estimate.md</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Estimate Module &gt; Meaning, status, and forms</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KB-0054</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Estimate Module</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Estimate Module</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>How do I prepare the header for an estimate?</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>To prepare the header, create an Estimates record and accept or enter its estimate number. Review the Quote Date, Expiration Date, and Status, link the relevant prospect or customer and contact, record the customer's quote reference if supplied, and review terms, currency, tax information, and order discount. Save the header before opening Estimate Lines.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>create estimate, quote date, expiration date, terms, tax code</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>estimate.md</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Estimate Module &gt; Prepare the header</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0055</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Estimate Module</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Estimate Module</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HELP_GENERIC</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>What is the purpose of the estimate header?</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>A valid header establishes quote identity, validity period, party, and commercial terms.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>create estimate, quote date, expiration date, terms</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>estimate.md</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Estimate Module &gt; Prepare the header</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0056</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Estimate Module</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Estimate Module</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>What should I review for each Estimate Line before issuing a quote?</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>For each Estimate Line, review the line number, item, Qty Ordered, U/M, status, Sales Disc, Unit Price, expected delivery, and sourcing details where shown. Also, review totals, taxes, margins, and feasibility before issuing a quote.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Estimate Lines, item, quantity, Unit Price, Sales Disc</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>estimate.md</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Estimate Module &gt; Prepare and review lines</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0057</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Estimate Module</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Estimate Module</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>What happens if I change the quantity on an Estimate Line?</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>If the line quantity changes, SyteLine may ask whether to recalculate price; record the answer because the quoted price may otherwise stay as it was.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Estimate Lines, quantity, price, quoted price</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>estimate.md</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Estimate Module &gt; Prepare and review lines</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KB-0058</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Estimate Module</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Estimate Module</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>What happens when I copy an accepted estimate to create an order?</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>When you use Copy Orders and Estimates to create an order from an accepted estimate, not every source value is preserved: historic values and calculated taxes may be recalculated, and some values come from current customer or tax configuration. You should review the new order header and every line before treating it as booked demand.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>copy estimate to order, accepted estimate, conversion, recalculated tax</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>estimate.md</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Estimate Module &gt; Handoff after acceptance</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -658,39 +1248,669 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>variation_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>question_variation</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>validated</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>KB-0052</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>What does an estimate contain?</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KB-0052</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Can you explain what an estimate is used for?</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KB-0052</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>What info is included in an estimate?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0053</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>What are the statuses for an estimate?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0053</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>What does Quoted status mean on an estimate?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0053</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Can you explain the estimate status options?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KB-0054</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>What steps are involved in setting up an estimate header?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KB-0054</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>How do I start an estimate and fill out the header?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KB-0054</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>What do I need to do to complete the estimate header?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KB-0055</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Why do I need an estimate header?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KB-0055</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>What does the estimate header define?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KB-0055</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>What's the role of the header in an estimate?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KB-0056</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>What details do I need to check on estimate lines?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KB-0056</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>How do I prepare estimate lines for a quote?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KB-0056</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>What should be reviewed on each estimate line?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KB-0057</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Does the price update if I change the estimate line quantity?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KB-0057</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>What should I do if I adjust the quantity on an estimate line?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KB-0057</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Will SyteLine recalculate price when quantity changes?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>KB-0058</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>How does copying an accepted estimate to an order work?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KB-0058</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>What should I check after converting an estimate to an order?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>KB-0058</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Does everything copy over when I turn an estimate into an order?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
